--- a/i_test/05_05_test_adding_PROMPT_T_and_LB/i_input_xlsx/Person_rel_PROMPT_dataset.xlsx
+++ b/i_test/05_05_test_adding_PROMPT_T_and_LB/i_input_xlsx/Person_rel_PROMPT_dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\giorg\GitHub\ConcePTIONAlgorithmPregnancies\i_test\05_05_test_adding_PROMPT_T_and_LB\i_input_xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F2E58E1-2E6E-4999-97AC-EA59AFDBB11B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBEA92F5-8D4B-413A-A806-04D560F1D778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13056" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="17">
   <si>
     <t>child_id</t>
   </si>
@@ -65,6 +65,12 @@
   </si>
   <si>
     <t>child_2_person_2</t>
+  </si>
+  <si>
+    <t>child_2_person_1</t>
+  </si>
+  <si>
+    <t>child_3_person_1</t>
   </si>
 </sst>
 </file>
@@ -405,7 +411,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.88671875" customWidth="1"/>
@@ -470,10 +476,10 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>6</v>
@@ -485,12 +491,64 @@
         <v>8</v>
       </c>
       <c r="F3" s="1">
+        <v>20181215</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="1">
+        <v>20181215</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="1">
         <v>20101215</v>
       </c>
-      <c r="G3" s="1">
-        <v>1</v>
-      </c>
-      <c r="H3" s="1">
+      <c r="G5" s="1">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1">
         <v>1</v>
       </c>
     </row>
